--- a/Results/Study 2/VGG11 (pretrained)/Confusion Matrices.xlsx
+++ b/Results/Study 2/VGG11 (pretrained)/Confusion Matrices.xlsx
@@ -400,10 +400,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>461</v>
+        <v>525</v>
       </c>
       <c r="C2">
-        <v>179</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -411,10 +411,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>154</v>
+        <v>500</v>
       </c>
       <c r="C3">
-        <v>486</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -440,10 +440,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C2">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -451,10 +451,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>63</v>
+        <v>123</v>
       </c>
       <c r="C3">
-        <v>97</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Study 2/VGG11 (pretrained)/Confusion Matrices.xlsx
+++ b/Results/Study 2/VGG11 (pretrained)/Confusion Matrices.xlsx
@@ -400,10 +400,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C2">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -411,10 +411,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="C3">
-        <v>140</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -451,10 +451,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
